--- a/Inventory.xlsx
+++ b/Inventory.xlsx
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CE014-0074</t>
         </is>
       </c>
       <c r="E49" t="n">

--- a/Inventory.xlsx
+++ b/Inventory.xlsx
@@ -4152,7 +4152,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PE003-0003-R03</t>
         </is>
       </c>
       <c r="E113" t="n">

--- a/Inventory.xlsx
+++ b/Inventory.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5858,6 +5858,36 @@
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
     </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Pendrive 32 GB</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>-----</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>4</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>G1-Office-Stationary Storage</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Inventory.xlsx
+++ b/Inventory.xlsx
@@ -5864,7 +5864,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Pendrive 32 GB</t>
+          <t>Pen Drive 32 GB</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">

--- a/Inventory.xlsx
+++ b/Inventory.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:H167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5888,6 +5888,32 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
     </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>254mm Lens Spacer SAV</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="n">
+        <v>1</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>G1-Storage-B2</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
